--- a/docs/ARCHIVE CDCH 2026.xlsx
+++ b/docs/ARCHIVE CDCH 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33caa50deb9c955e/ARCHILBO/PROJETS/ARCHIVE CAHIER DE CHANTIER/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARCHI LBO\LBOSM\LBOCRM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_B70968793FA70543D855D051A0FD43F63C324FBD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C8F6221-CB6E-4751-9988-4212AC8C8CF3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07E7DDE-C366-4415-BCFC-899F1FC611FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MARRAKECH" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="KELAA" sheetId="5" r:id="rId5"/>
     <sheet name="AGADIR" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -6776,6 +6775,9 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6785,19 +6787,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6824,7 +6823,10 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6839,10 +6841,7 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6854,9 +6853,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6864,6 +6860,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6880,7 +6879,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Milliers" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -7174,86 +7173,86 @@
     <tabColor rgb="FFB3D2FB"/>
   </sheetPr>
   <dimension ref="A1:LB97"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" customWidth="1"/>
-    <col min="2" max="2" width="71.81640625" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" customWidth="1"/>
-    <col min="4" max="4" width="22.453125" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" customWidth="1"/>
-    <col min="6" max="6" width="65.81640625" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="26.81640625" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="71.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="65.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" customWidth="1"/>
     <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" customWidth="1"/>
-    <col min="11" max="11" width="15.81640625" customWidth="1"/>
-    <col min="12" max="13" width="15.54296875" style="57" customWidth="1"/>
-    <col min="14" max="14" width="15.1796875" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" customWidth="1"/>
-    <col min="16" max="16" width="12.81640625" customWidth="1"/>
-    <col min="17" max="17" width="15.54296875" customWidth="1"/>
-    <col min="18" max="18" width="17.1796875" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" customWidth="1"/>
-    <col min="20" max="20" width="12.81640625" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="13" width="15.5703125" style="57" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" customWidth="1"/>
-    <col min="23" max="23" width="12.453125" customWidth="1"/>
-    <col min="24" max="24" width="13.54296875" customWidth="1"/>
-    <col min="25" max="25" width="11.1796875" customWidth="1"/>
-    <col min="26" max="27" width="10.453125" customWidth="1"/>
-    <col min="28" max="28" width="11.54296875" customWidth="1"/>
-    <col min="29" max="29" width="32.1796875" customWidth="1"/>
-    <col min="30" max="30" width="31.1796875" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" customWidth="1"/>
+    <col min="23" max="23" width="12.42578125" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" customWidth="1"/>
+    <col min="25" max="25" width="11.140625" customWidth="1"/>
+    <col min="26" max="27" width="10.42578125" customWidth="1"/>
+    <col min="28" max="28" width="11.5703125" customWidth="1"/>
+    <col min="29" max="29" width="32.140625" customWidth="1"/>
+    <col min="30" max="30" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="25" x14ac:dyDescent="0.5">
-      <c r="A1" s="217"/>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="217"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="217"/>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="217"/>
-      <c r="AA1" s="217"/>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="217"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="212"/>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
+      <c r="T1" s="212"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
+      <c r="W1" s="212"/>
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212"/>
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="212"/>
+      <c r="AB1" s="212"/>
+      <c r="AC1" s="212"/>
+      <c r="AD1" s="212"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="L2"/>
       <c r="M2"/>
     </row>
-    <row r="3" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="216" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="216" t="s">
         <v>1044</v>
       </c>
-      <c r="C3" s="212" t="s">
+      <c r="C3" s="213" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="213"/>
-      <c r="E3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="215"/>
       <c r="F3" s="216" t="s">
         <v>2</v>
       </c>
@@ -7272,37 +7271,37 @@
       <c r="K3" s="216" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="215" t="s">
+      <c r="L3" s="219" t="s">
         <v>1260</v>
       </c>
-      <c r="M3" s="218" t="s">
+      <c r="M3" s="217" t="s">
         <v>1261</v>
       </c>
-      <c r="N3" s="212" t="s">
+      <c r="N3" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="213"/>
-      <c r="P3" s="214"/>
-      <c r="Q3" s="212" t="s">
+      <c r="O3" s="214"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="213" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="213"/>
-      <c r="S3" s="214"/>
-      <c r="T3" s="212" t="s">
+      <c r="R3" s="214"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="U3" s="213"/>
-      <c r="V3" s="214"/>
-      <c r="W3" s="212" t="s">
+      <c r="U3" s="214"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="213" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="213"/>
-      <c r="Y3" s="214"/>
-      <c r="Z3" s="212" t="s">
+      <c r="X3" s="214"/>
+      <c r="Y3" s="215"/>
+      <c r="Z3" s="213" t="s">
         <v>13</v>
       </c>
-      <c r="AA3" s="213"/>
-      <c r="AB3" s="214"/>
+      <c r="AA3" s="214"/>
+      <c r="AB3" s="215"/>
       <c r="AC3" s="216" t="s">
         <v>14</v>
       </c>
@@ -7310,7 +7309,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="216"/>
       <c r="B4" s="216"/>
       <c r="C4" s="4" t="s">
@@ -7328,8 +7327,8 @@
       <c r="I4" s="216"/>
       <c r="J4" s="216"/>
       <c r="K4" s="216"/>
-      <c r="L4" s="215"/>
-      <c r="M4" s="219"/>
+      <c r="L4" s="219"/>
+      <c r="M4" s="218"/>
       <c r="N4" s="4" t="s">
         <v>1</v>
       </c>
@@ -7378,7 +7377,7 @@
       <c r="AC4" s="216"/>
       <c r="AD4" s="216"/>
     </row>
-    <row r="5" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
@@ -7427,7 +7426,7 @@
       </c>
       <c r="AD5" s="5"/>
     </row>
-    <row r="6" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>27</v>
       </c>
@@ -7476,7 +7475,7 @@
       </c>
       <c r="AD6" s="5"/>
     </row>
-    <row r="7" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>28</v>
       </c>
@@ -7523,7 +7522,7 @@
       </c>
       <c r="AD7" s="5"/>
     </row>
-    <row r="8" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>29</v>
       </c>
@@ -7572,7 +7571,7 @@
       </c>
       <c r="AD8" s="5"/>
     </row>
-    <row r="9" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>30</v>
       </c>
@@ -7621,7 +7620,7 @@
       </c>
       <c r="AD9" s="5"/>
     </row>
-    <row r="10" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>31</v>
       </c>
@@ -7674,7 +7673,7 @@
       </c>
       <c r="AD10" s="5"/>
     </row>
-    <row r="11" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>32</v>
       </c>
@@ -7723,7 +7722,7 @@
       </c>
       <c r="AD11" s="5"/>
     </row>
-    <row r="12" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
@@ -7772,7 +7771,7 @@
       </c>
       <c r="AD12" s="5"/>
     </row>
-    <row r="13" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
@@ -7821,7 +7820,7 @@
       </c>
       <c r="AD13" s="5"/>
     </row>
-    <row r="14" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>35</v>
       </c>
@@ -7876,7 +7875,7 @@
       </c>
       <c r="AD14" s="5"/>
     </row>
-    <row r="15" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>36</v>
       </c>
@@ -7925,7 +7924,7 @@
       </c>
       <c r="AD15" s="5"/>
     </row>
-    <row r="16" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>37</v>
       </c>
@@ -7974,7 +7973,7 @@
       </c>
       <c r="AD16" s="5"/>
     </row>
-    <row r="17" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>38</v>
       </c>
@@ -8031,7 +8030,7 @@
       </c>
       <c r="AD17" s="5"/>
     </row>
-    <row r="18" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>39</v>
       </c>
@@ -8080,7 +8079,7 @@
       </c>
       <c r="AD18" s="5"/>
     </row>
-    <row r="19" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>40</v>
       </c>
@@ -8129,7 +8128,7 @@
       </c>
       <c r="AD19" s="5"/>
     </row>
-    <row r="20" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>41</v>
       </c>
@@ -8178,7 +8177,7 @@
       </c>
       <c r="AD20" s="5"/>
     </row>
-    <row r="21" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>42</v>
       </c>
@@ -8231,7 +8230,7 @@
       </c>
       <c r="AD21" s="5"/>
     </row>
-    <row r="22" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>43</v>
       </c>
@@ -8288,7 +8287,7 @@
       </c>
       <c r="AD22" s="5"/>
     </row>
-    <row r="23" spans="1:30" s="69" customFormat="1" ht="80.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" s="69" customFormat="1" ht="80.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>44</v>
       </c>
@@ -8346,7 +8345,7 @@
       </c>
       <c r="AD23" s="5"/>
     </row>
-    <row r="24" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="139" t="s">
         <v>45</v>
       </c>
@@ -8409,7 +8408,7 @@
       </c>
       <c r="AD24" s="5"/>
     </row>
-    <row r="25" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>46</v>
       </c>
@@ -8472,7 +8471,7 @@
       </c>
       <c r="AD25" s="5"/>
     </row>
-    <row r="26" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>47</v>
       </c>
@@ -8522,7 +8521,7 @@
       </c>
       <c r="AD26" s="5"/>
     </row>
-    <row r="27" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>48</v>
       </c>
@@ -8565,7 +8564,7 @@
       </c>
       <c r="AD27" s="5"/>
     </row>
-    <row r="28" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>49</v>
       </c>
@@ -8631,7 +8630,7 @@
       </c>
       <c r="AD28" s="5"/>
     </row>
-    <row r="29" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>317</v>
       </c>
@@ -8672,7 +8671,7 @@
       </c>
       <c r="AD29" s="5"/>
     </row>
-    <row r="30" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>318</v>
       </c>
@@ -8713,7 +8712,7 @@
       </c>
       <c r="AD30" s="5"/>
     </row>
-    <row r="31" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>319</v>
       </c>
@@ -8754,7 +8753,7 @@
       </c>
       <c r="AD31" s="5"/>
     </row>
-    <row r="32" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>21</v>
       </c>
@@ -8817,7 +8816,7 @@
       </c>
       <c r="AD32" s="5"/>
     </row>
-    <row r="33" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>320</v>
       </c>
@@ -8858,7 +8857,7 @@
       </c>
       <c r="AD33" s="5"/>
     </row>
-    <row r="34" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>321</v>
       </c>
@@ -8907,7 +8906,7 @@
       </c>
       <c r="AD34" s="5"/>
     </row>
-    <row r="35" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="139" t="s">
         <v>322</v>
       </c>
@@ -8964,7 +8963,7 @@
       </c>
       <c r="AD35" s="5"/>
     </row>
-    <row r="36" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>323</v>
       </c>
@@ -9005,7 +9004,7 @@
       </c>
       <c r="AD36" s="5"/>
     </row>
-    <row r="37" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>324</v>
       </c>
@@ -9046,7 +9045,7 @@
       </c>
       <c r="AD37" s="5"/>
     </row>
-    <row r="38" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>325</v>
       </c>
@@ -9089,7 +9088,7 @@
       </c>
       <c r="AD38" s="5"/>
     </row>
-    <row r="39" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>326</v>
       </c>
@@ -9130,7 +9129,7 @@
       </c>
       <c r="AD39" s="5"/>
     </row>
-    <row r="40" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="139" t="s">
         <v>327</v>
       </c>
@@ -9193,7 +9192,7 @@
       </c>
       <c r="AD40" s="5"/>
     </row>
-    <row r="41" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>328</v>
       </c>
@@ -9256,7 +9255,7 @@
       </c>
       <c r="AD41" s="5"/>
     </row>
-    <row r="42" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>329</v>
       </c>
@@ -9297,7 +9296,7 @@
       </c>
       <c r="AD42" s="5"/>
     </row>
-    <row r="43" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>330</v>
       </c>
@@ -9343,7 +9342,7 @@
       </c>
       <c r="AD43" s="5"/>
     </row>
-    <row r="44" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>331</v>
       </c>
@@ -9384,7 +9383,7 @@
       </c>
       <c r="AD44" s="5"/>
     </row>
-    <row r="45" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>332</v>
       </c>
@@ -9425,7 +9424,7 @@
       </c>
       <c r="AD45" s="5"/>
     </row>
-    <row r="46" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>333</v>
       </c>
@@ -9466,7 +9465,7 @@
       </c>
       <c r="AD46" s="5"/>
     </row>
-    <row r="47" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="114" t="s">
         <v>334</v>
       </c>
@@ -9523,7 +9522,7 @@
       </c>
       <c r="AD47" s="117"/>
     </row>
-    <row r="48" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A48" s="106" t="s">
         <v>335</v>
       </c>
@@ -9594,7 +9593,7 @@
       </c>
       <c r="AD48" s="68"/>
     </row>
-    <row r="49" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>336</v>
       </c>
@@ -9635,7 +9634,7 @@
       </c>
       <c r="AD49" s="5"/>
     </row>
-    <row r="50" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>337</v>
       </c>
@@ -9694,7 +9693,7 @@
       </c>
       <c r="AD50" s="5"/>
     </row>
-    <row r="51" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>338</v>
       </c>
@@ -9751,7 +9750,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="52" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>339</v>
       </c>
@@ -9794,7 +9793,7 @@
       </c>
       <c r="AD52" s="5"/>
     </row>
-    <row r="53" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>340</v>
       </c>
@@ -9839,7 +9838,7 @@
       </c>
       <c r="AD53" s="5"/>
     </row>
-    <row r="54" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>341</v>
       </c>
@@ -9894,7 +9893,7 @@
       </c>
       <c r="AD54" s="5"/>
     </row>
-    <row r="55" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>15</v>
       </c>
@@ -9957,7 +9956,7 @@
       </c>
       <c r="AD55" s="5"/>
     </row>
-    <row r="56" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>342</v>
       </c>
@@ -10013,7 +10012,7 @@
       </c>
       <c r="AD56" s="5"/>
     </row>
-    <row r="57" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>343</v>
       </c>
@@ -10058,7 +10057,7 @@
       </c>
       <c r="AD57" s="5"/>
     </row>
-    <row r="58" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>344</v>
       </c>
@@ -10109,7 +10108,7 @@
       </c>
       <c r="AD58" s="5"/>
     </row>
-    <row r="59" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>345</v>
       </c>
@@ -10148,7 +10147,7 @@
       </c>
       <c r="AD59" s="5"/>
     </row>
-    <row r="60" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
         <v>346</v>
       </c>
@@ -10187,7 +10186,7 @@
       </c>
       <c r="AD60" s="5"/>
     </row>
-    <row r="61" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>347</v>
       </c>
@@ -10239,7 +10238,7 @@
       </c>
       <c r="AD61" s="5"/>
     </row>
-    <row r="62" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
         <v>348</v>
       </c>
@@ -10278,7 +10277,7 @@
       </c>
       <c r="AD62" s="5"/>
     </row>
-    <row r="63" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="139" t="s">
         <v>349</v>
       </c>
@@ -10335,7 +10334,7 @@
       </c>
       <c r="AD63" s="5"/>
     </row>
-    <row r="64" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="139" t="s">
         <v>350</v>
       </c>
@@ -10392,7 +10391,7 @@
       </c>
       <c r="AD64" s="5"/>
     </row>
-    <row r="65" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="139" t="s">
         <v>351</v>
       </c>
@@ -10449,7 +10448,7 @@
       </c>
       <c r="AD65" s="5"/>
     </row>
-    <row r="66" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
         <v>352</v>
       </c>
@@ -10514,7 +10513,7 @@
       </c>
       <c r="AD66" s="5"/>
     </row>
-    <row r="67" spans="1:314" s="180" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:314" s="180" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="183" t="s">
         <v>353</v>
       </c>
@@ -10865,7 +10864,7 @@
       <c r="LA67" s="69"/>
       <c r="LB67" s="69"/>
     </row>
-    <row r="68" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="139" t="s">
         <v>354</v>
       </c>
@@ -10934,7 +10933,7 @@
       </c>
       <c r="AD68" s="5"/>
     </row>
-    <row r="69" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="139" t="s">
         <v>355</v>
       </c>
@@ -10997,7 +10996,7 @@
       </c>
       <c r="AD69" s="5"/>
     </row>
-    <row r="70" spans="1:314" s="69" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:314" s="69" customFormat="1" ht="90.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
         <v>356</v>
       </c>
@@ -11071,7 +11070,7 @@
       </c>
       <c r="AD70" s="5"/>
     </row>
-    <row r="71" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>1262</v>
       </c>
@@ -11134,7 +11133,7 @@
       </c>
       <c r="AD71" s="5"/>
     </row>
-    <row r="72" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
         <v>357</v>
       </c>
@@ -11193,7 +11192,7 @@
       </c>
       <c r="AD72" s="5"/>
     </row>
-    <row r="73" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>358</v>
       </c>
@@ -11248,7 +11247,7 @@
       </c>
       <c r="AD73" s="5"/>
     </row>
-    <row r="74" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="139" t="s">
         <v>359</v>
       </c>
@@ -11313,7 +11312,7 @@
       </c>
       <c r="AD74" s="5"/>
     </row>
-    <row r="75" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
         <v>360</v>
       </c>
@@ -11366,7 +11365,7 @@
       </c>
       <c r="AD75" s="5"/>
     </row>
-    <row r="76" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="139" t="s">
         <v>361</v>
       </c>
@@ -11434,7 +11433,7 @@
       </c>
       <c r="AD76" s="5"/>
     </row>
-    <row r="77" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>362</v>
       </c>
@@ -11485,7 +11484,7 @@
       </c>
       <c r="AD77" s="5"/>
     </row>
-    <row r="78" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
         <v>363</v>
       </c>
@@ -11532,7 +11531,7 @@
       </c>
       <c r="AD78" s="5"/>
     </row>
-    <row r="79" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>364</v>
       </c>
@@ -11597,7 +11596,7 @@
       </c>
       <c r="AD79" s="5"/>
     </row>
-    <row r="80" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:314" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
         <v>365</v>
       </c>
@@ -11644,7 +11643,7 @@
       </c>
       <c r="AD80" s="5"/>
     </row>
-    <row r="81" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>366</v>
       </c>
@@ -11693,7 +11692,7 @@
       </c>
       <c r="AD81" s="5"/>
     </row>
-    <row r="82" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
         <v>367</v>
       </c>
@@ -11746,7 +11745,7 @@
       </c>
       <c r="AD82" s="76"/>
     </row>
-    <row r="83" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
         <v>368</v>
       </c>
@@ -11791,7 +11790,7 @@
       </c>
       <c r="AD83" s="5"/>
     </row>
-    <row r="84" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
         <v>369</v>
       </c>
@@ -11834,7 +11833,7 @@
       </c>
       <c r="AD84" s="5"/>
     </row>
-    <row r="85" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
         <v>370</v>
       </c>
@@ -11881,7 +11880,7 @@
       </c>
       <c r="AD85" s="5"/>
     </row>
-    <row r="86" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="13" t="s">
         <v>371</v>
       </c>
@@ -11926,7 +11925,7 @@
       </c>
       <c r="AD86" s="5"/>
     </row>
-    <row r="87" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:30" s="69" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
         <v>1361</v>
       </c>
@@ -11975,7 +11974,7 @@
       </c>
       <c r="AD87" s="5"/>
     </row>
-    <row r="88" spans="1:30" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:30" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
         <v>1362</v>
       </c>
@@ -12026,7 +12025,7 @@
       </c>
       <c r="AD88" s="1"/>
     </row>
-    <row r="89" spans="1:30" ht="50.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:30" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
         <v>1363</v>
       </c>
@@ -12080,7 +12079,7 @@
       </c>
       <c r="AD89" s="1"/>
     </row>
-    <row r="90" spans="1:30" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:30" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
         <v>1364</v>
       </c>
@@ -12128,7 +12127,7 @@
       </c>
       <c r="AD90" s="1"/>
     </row>
-    <row r="91" spans="1:30" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:30" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
         <v>1365</v>
       </c>
@@ -12182,7 +12181,7 @@
       </c>
       <c r="AD91" s="1"/>
     </row>
-    <row r="92" spans="1:30" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:30" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
         <v>1366</v>
       </c>
@@ -12224,7 +12223,7 @@
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
     </row>
-    <row r="93" spans="1:30" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:30" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
         <v>1367</v>
       </c>
@@ -12262,7 +12261,7 @@
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
     </row>
-    <row r="94" spans="1:30" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:30" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
         <v>1368</v>
       </c>
@@ -12304,7 +12303,7 @@
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
     </row>
-    <row r="95" spans="1:30" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:30" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
         <v>1369</v>
       </c>
@@ -12338,7 +12337,7 @@
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
     </row>
-    <row r="96" spans="1:30" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:30" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
         <v>1370</v>
       </c>
@@ -12372,7 +12371,7 @@
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
     </row>
-    <row r="97" spans="1:30" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:30" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>1374</v>
       </c>
@@ -12411,6 +12410,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
     <mergeCell ref="A1:AD1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="AD3:AD4"/>
@@ -12427,9 +12429,6 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12442,38 +12441,38 @@
     <tabColor rgb="FFF2BCE3"/>
   </sheetPr>
   <dimension ref="A1:AD284"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.1796875" customWidth="1"/>
-    <col min="3" max="5" width="13.81640625" customWidth="1"/>
-    <col min="6" max="6" width="33.1796875" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" customWidth="1"/>
-    <col min="8" max="8" width="34.54296875" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" customWidth="1"/>
-    <col min="11" max="11" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" customWidth="1"/>
+    <col min="3" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="34.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" customWidth="1"/>
     <col min="12" max="12" width="14" style="57" customWidth="1"/>
     <col min="13" max="13" width="14" style="162" customWidth="1"/>
-    <col min="14" max="14" width="14.54296875" customWidth="1"/>
-    <col min="15" max="15" width="13.26953125" customWidth="1"/>
-    <col min="16" max="16" width="13.453125" customWidth="1"/>
-    <col min="17" max="17" width="13.1796875" customWidth="1"/>
-    <col min="18" max="18" width="10.1796875" customWidth="1"/>
-    <col min="19" max="19" width="14.453125" customWidth="1"/>
-    <col min="20" max="22" width="15.54296875" customWidth="1"/>
-    <col min="23" max="23" width="13.1796875" customWidth="1"/>
-    <col min="24" max="24" width="10.81640625" customWidth="1"/>
-    <col min="25" max="25" width="13.54296875" customWidth="1"/>
-    <col min="26" max="26" width="14.54296875" customWidth="1"/>
-    <col min="27" max="27" width="10.453125" customWidth="1"/>
-    <col min="28" max="28" width="10.81640625" customWidth="1"/>
-    <col min="29" max="29" width="11.1796875" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" customWidth="1"/>
+    <col min="20" max="22" width="15.5703125" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" customWidth="1"/>
+    <col min="24" max="24" width="10.85546875" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" customWidth="1"/>
+    <col min="28" max="28" width="10.85546875" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L1"/>
     </row>
-    <row r="2" spans="1:30" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="220" t="s">
         <v>0</v>
       </c>
@@ -12541,7 +12540,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="220"/>
       <c r="B3" s="220"/>
       <c r="C3" s="14" t="s">
@@ -12609,7 +12608,7 @@
       <c r="AC3" s="220"/>
       <c r="AD3" s="220"/>
     </row>
-    <row r="4" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>50</v>
       </c>
@@ -12652,7 +12651,7 @@
       </c>
       <c r="AD4" s="5"/>
     </row>
-    <row r="5" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
@@ -12691,7 +12690,7 @@
       </c>
       <c r="AD5" s="5"/>
     </row>
-    <row r="6" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>52</v>
       </c>
@@ -12730,7 +12729,7 @@
       </c>
       <c r="AD6" s="5"/>
     </row>
-    <row r="7" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
@@ -12773,7 +12772,7 @@
       </c>
       <c r="AD7" s="5"/>
     </row>
-    <row r="8" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>54</v>
       </c>
@@ -12814,7 +12813,7 @@
       </c>
       <c r="AD8" s="5"/>
     </row>
-    <row r="9" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>55</v>
       </c>
@@ -12859,7 +12858,7 @@
       </c>
       <c r="AD9" s="5"/>
     </row>
-    <row r="10" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>56</v>
       </c>
@@ -12898,7 +12897,7 @@
       </c>
       <c r="AD10" s="5"/>
     </row>
-    <row r="11" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>57</v>
       </c>
@@ -12941,7 +12940,7 @@
       </c>
       <c r="AD11" s="5"/>
     </row>
-    <row r="12" spans="1:30" s="69" customFormat="1" ht="110.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" s="69" customFormat="1" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>58</v>
       </c>
@@ -13020,7 +13019,7 @@
       </c>
       <c r="AD12" s="8"/>
     </row>
-    <row r="13" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>59</v>
       </c>
@@ -13063,7 +13062,7 @@
       </c>
       <c r="AD13" s="5"/>
     </row>
-    <row r="14" spans="1:30" s="69" customFormat="1" ht="92.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" s="69" customFormat="1" ht="92.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>60</v>
       </c>
@@ -13134,7 +13133,7 @@
       </c>
       <c r="AD14" s="5"/>
     </row>
-    <row r="15" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>61</v>
       </c>
@@ -13177,7 +13176,7 @@
       </c>
       <c r="AD15" s="5"/>
     </row>
-    <row r="16" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>62</v>
       </c>
@@ -13220,7 +13219,7 @@
       </c>
       <c r="AD16" s="5"/>
     </row>
-    <row r="17" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>63</v>
       </c>
@@ -13263,7 +13262,7 @@
       </c>
       <c r="AD17" s="5"/>
     </row>
-    <row r="18" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>64</v>
       </c>
@@ -13306,7 +13305,7 @@
       </c>
       <c r="AD18" s="5"/>
     </row>
-    <row r="19" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>657</v>
       </c>
@@ -13349,7 +13348,7 @@
       </c>
       <c r="AD19" s="5"/>
     </row>
-    <row r="20" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>658</v>
       </c>
@@ -13394,7 +13393,7 @@
       </c>
       <c r="AD20" s="5"/>
     </row>
-    <row r="21" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>659</v>
       </c>
@@ -13437,7 +13436,7 @@
       </c>
       <c r="AD21" s="5"/>
     </row>
-    <row r="22" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>660</v>
       </c>
@@ -13480,7 +13479,7 @@
       </c>
       <c r="AD22" s="5"/>
     </row>
-    <row r="23" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>661</v>
       </c>
@@ -13523,7 +13522,7 @@
       </c>
       <c r="AD23" s="5"/>
     </row>
-    <row r="24" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>662</v>
       </c>
@@ -13566,7 +13565,7 @@
       </c>
       <c r="AD24" s="5"/>
     </row>
-    <row r="25" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>663</v>
       </c>
@@ -13609,7 +13608,7 @@
       </c>
       <c r="AD25" s="5"/>
     </row>
-    <row r="26" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>664</v>
       </c>
@@ -13652,7 +13651,7 @@
       </c>
       <c r="AD26" s="5"/>
     </row>
-    <row r="27" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>665</v>
       </c>
@@ -13695,7 +13694,7 @@
       </c>
       <c r="AD27" s="5"/>
     </row>
-    <row r="28" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>666</v>
       </c>
@@ -13738,7 +13737,7 @@
       </c>
       <c r="AD28" s="5"/>
     </row>
-    <row r="29" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>667</v>
       </c>
@@ -13777,7 +13776,7 @@
       </c>
       <c r="AD29" s="5"/>
     </row>
-    <row r="30" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>668</v>
       </c>
@@ -13826,7 +13825,7 @@
       </c>
       <c r="AD30" s="5"/>
     </row>
-    <row r="31" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>669</v>
       </c>
@@ -13877,7 +13876,7 @@
       </c>
       <c r="AD31" s="5"/>
     </row>
-    <row r="32" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>670</v>
       </c>
@@ -13920,7 +13919,7 @@
       </c>
       <c r="AD32" s="5"/>
     </row>
-    <row r="33" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>671</v>
       </c>
@@ -13963,7 +13962,7 @@
       </c>
       <c r="AD33" s="5"/>
     </row>
-    <row r="34" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>672</v>
       </c>
@@ -14006,7 +14005,7 @@
       </c>
       <c r="AD34" s="5"/>
     </row>
-    <row r="35" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>673</v>
       </c>
@@ -14049,7 +14048,7 @@
       </c>
       <c r="AD35" s="5"/>
     </row>
-    <row r="36" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>674</v>
       </c>
@@ -14092,7 +14091,7 @@
       </c>
       <c r="AD36" s="5"/>
     </row>
-    <row r="37" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>675</v>
       </c>
@@ -14135,7 +14134,7 @@
       </c>
       <c r="AD37" s="5"/>
     </row>
-    <row r="38" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>676</v>
       </c>
@@ -14174,7 +14173,7 @@
       </c>
       <c r="AD38" s="5"/>
     </row>
-    <row r="39" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>677</v>
       </c>
@@ -14217,7 +14216,7 @@
       </c>
       <c r="AD39" s="5"/>
     </row>
-    <row r="40" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>678</v>
       </c>
@@ -14260,7 +14259,7 @@
       </c>
       <c r="AD40" s="5"/>
     </row>
-    <row r="41" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>679</v>
       </c>
@@ -14303,7 +14302,7 @@
       </c>
       <c r="AD41" s="5"/>
     </row>
-    <row r="42" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>680</v>
       </c>
@@ -14342,7 +14341,7 @@
       </c>
       <c r="AD42" s="5"/>
     </row>
-    <row r="43" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>681</v>
       </c>
@@ -14385,7 +14384,7 @@
       </c>
       <c r="AD43" s="5"/>
     </row>
-    <row r="44" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>682</v>
       </c>
@@ -14424,7 +14423,7 @@
       </c>
       <c r="AD44" s="5"/>
     </row>
-    <row r="45" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>683</v>
       </c>
@@ -14467,7 +14466,7 @@
       </c>
       <c r="AD45" s="5"/>
     </row>
-    <row r="46" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>684</v>
       </c>
@@ -14510,7 +14509,7 @@
       </c>
       <c r="AD46" s="5"/>
     </row>
-    <row r="47" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>685</v>
       </c>
@@ -14555,7 +14554,7 @@
       </c>
       <c r="AD47" s="5"/>
     </row>
-    <row r="48" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>686</v>
       </c>
@@ -14600,7 +14599,7 @@
       </c>
       <c r="AD48" s="5"/>
     </row>
-    <row r="49" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
         <v>687</v>
       </c>
@@ -14645,7 +14644,7 @@
       </c>
       <c r="AD49" s="5"/>
     </row>
-    <row r="50" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>688</v>
       </c>
@@ -14690,7 +14689,7 @@
       </c>
       <c r="AD50" s="5"/>
     </row>
-    <row r="51" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
         <v>689</v>
       </c>
@@ -14735,7 +14734,7 @@
       </c>
       <c r="AD51" s="5"/>
     </row>
-    <row r="52" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
         <v>690</v>
       </c>
@@ -14778,7 +14777,7 @@
       </c>
       <c r="AD52" s="5"/>
     </row>
-    <row r="53" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>691</v>
       </c>
@@ -14821,7 +14820,7 @@
       </c>
       <c r="AD53" s="5"/>
     </row>
-    <row r="54" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="15" t="s">
         <v>692</v>
       </c>
@@ -14860,7 +14859,7 @@
       </c>
       <c r="AD54" s="5"/>
     </row>
-    <row r="55" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
         <v>693</v>
       </c>
@@ -14903,7 +14902,7 @@
       </c>
       <c r="AD55" s="5"/>
     </row>
-    <row r="56" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
         <v>694</v>
       </c>
@@ -14946,7 +14945,7 @@
       </c>
       <c r="AD56" s="5"/>
     </row>
-    <row r="57" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
         <v>695</v>
       </c>
@@ -14989,7 +14988,7 @@
       </c>
       <c r="AD57" s="5"/>
     </row>
-    <row r="58" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>696</v>
       </c>
@@ -15028,7 +15027,7 @@
       </c>
       <c r="AD58" s="5"/>
     </row>
-    <row r="59" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>697</v>
       </c>
@@ -15071,7 +15070,7 @@
       </c>
       <c r="AD59" s="5"/>
     </row>
-    <row r="60" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>698</v>
       </c>
@@ -15110,7 +15109,7 @@
       </c>
       <c r="AD60" s="5"/>
     </row>
-    <row r="61" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>699</v>
       </c>
@@ -15153,7 +15152,7 @@
       </c>
       <c r="AD61" s="5"/>
     </row>
-    <row r="62" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>700</v>
       </c>
@@ -15202,7 +15201,7 @@
       </c>
       <c r="AD62" s="5"/>
     </row>
-    <row r="63" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
         <v>701</v>
       </c>
@@ -15245,7 +15244,7 @@
       </c>
       <c r="AD63" s="5"/>
     </row>
-    <row r="64" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
         <v>702</v>
       </c>
@@ -15288,7 +15287,7 @@
       </c>
       <c r="AD64" s="5"/>
     </row>
-    <row r="65" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
         <v>703</v>
       </c>
@@ -15327,7 +15326,7 @@
       </c>
       <c r="AD65" s="5"/>
     </row>
-    <row r="66" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
         <v>704</v>
       </c>
@@ -15370,7 +15369,7 @@
       </c>
       <c r="AD66" s="5"/>
     </row>
-    <row r="67" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
         <v>705</v>
       </c>
@@ -15415,7 +15414,7 @@
       </c>
       <c r="AD67" s="5"/>
     </row>
-    <row r="68" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
         <v>706</v>
       </c>
@@ -15460,7 +15459,7 @@
       </c>
       <c r="AD68" s="5"/>
     </row>
-    <row r="69" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
         <v>707</v>
       </c>
@@ -15503,7 +15502,7 @@
       </c>
       <c r="AD69" s="5"/>
     </row>
-    <row r="70" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
         <v>708</v>
       </c>
@@ -15548,7 +15547,7 @@
       </c>
       <c r="AD70" s="5"/>
     </row>
-    <row r="71" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
         <v>709</v>
       </c>
@@ -15587,7 +15586,7 @@
       </c>
       <c r="AD71" s="5"/>
     </row>
-    <row r="72" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
         <v>710</v>
       </c>
@@ -15630,7 +15629,7 @@
       </c>
       <c r="AD72" s="5"/>
     </row>
-    <row r="73" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>711</v>
       </c>
@@ -15673,7 +15672,7 @@
       </c>
       <c r="AD73" s="5"/>
     </row>
-    <row r="74" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>712</v>
       </c>
@@ -15716,7 +15715,7 @@
       </c>
       <c r="AD74" s="5"/>
     </row>
-    <row r="75" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
         <v>713</v>
       </c>
@@ -15755,7 +15754,7 @@
       </c>
       <c r="AD75" s="5"/>
     </row>
-    <row r="76" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
         <v>714</v>
       </c>
@@ -15798,7 +15797,7 @@
       </c>
       <c r="AD76" s="5"/>
     </row>
-    <row r="77" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
         <v>715</v>
       </c>
@@ -15841,7 +15840,7 @@
       </c>
       <c r="AD77" s="5"/>
     </row>
-    <row r="78" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
         <v>716</v>
       </c>
@@ -15880,7 +15879,7 @@
       </c>
       <c r="AD78" s="5"/>
     </row>
-    <row r="79" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
         <v>717</v>
       </c>
@@ -15923,7 +15922,7 @@
       </c>
       <c r="AD79" s="5"/>
     </row>
-    <row r="80" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
         <v>718</v>
       </c>
@@ -15966,7 +15965,7 @@
       </c>
       <c r="AD80" s="5"/>
     </row>
-    <row r="81" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
         <v>719</v>
       </c>
@@ -16009,7 +16008,7 @@
       </c>
       <c r="AD81" s="5"/>
     </row>
-    <row r="82" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
         <v>720</v>
       </c>
@@ -16052,7 +16051,7 @@
       </c>
       <c r="AD82" s="5"/>
     </row>
-    <row r="83" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
         <v>721</v>
       </c>
@@ -16095,7 +16094,7 @@
       </c>
       <c r="AD83" s="5"/>
     </row>
-    <row r="84" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
         <v>722</v>
       </c>
@@ -16138,7 +16137,7 @@
       </c>
       <c r="AD84" s="5"/>
     </row>
-    <row r="85" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
         <v>723</v>
       </c>
@@ -16181,7 +16180,7 @@
       </c>
       <c r="AD85" s="5"/>
     </row>
-    <row r="86" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
         <v>724</v>
       </c>
@@ -16224,7 +16223,7 @@
       </c>
       <c r="AD86" s="5"/>
     </row>
-    <row r="87" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
         <v>725</v>
       </c>
@@ -16267,7 +16266,7 @@
       </c>
       <c r="AD87" s="5"/>
     </row>
-    <row r="88" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
         <v>726</v>
       </c>
@@ -16310,7 +16309,7 @@
       </c>
       <c r="AD88" s="5"/>
     </row>
-    <row r="89" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
         <v>727</v>
       </c>
@@ -16353,7 +16352,7 @@
       </c>
       <c r="AD89" s="5"/>
     </row>
-    <row r="90" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
         <v>728</v>
       </c>
@@ -16396,7 +16395,7 @@
       </c>
       <c r="AD90" s="5"/>
     </row>
-    <row r="91" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
         <v>729</v>
       </c>
@@ -16439,7 +16438,7 @@
       </c>
       <c r="AD91" s="5"/>
     </row>
-    <row r="92" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="15" t="s">
         <v>730</v>
       </c>
@@ -16482,7 +16481,7 @@
       </c>
       <c r="AD92" s="5"/>
     </row>
-    <row r="93" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
         <v>731</v>
       </c>
@@ -16525,7 +16524,7 @@
       </c>
       <c r="AD93" s="5"/>
     </row>
-    <row r="94" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
         <v>732</v>
       </c>
@@ -16568,7 +16567,7 @@
       </c>
       <c r="AD94" s="5"/>
     </row>
-    <row r="95" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
         <v>733</v>
       </c>
@@ -16607,7 +16606,7 @@
       </c>
       <c r="AD95" s="5"/>
     </row>
-    <row r="96" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
         <v>734</v>
       </c>
@@ -16650,7 +16649,7 @@
       </c>
       <c r="AD96" s="5"/>
     </row>
-    <row r="97" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
         <v>735</v>
       </c>
@@ -16693,7 +16692,7 @@
       </c>
       <c r="AD97" s="5"/>
     </row>
-    <row r="98" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
         <v>736</v>
       </c>
@@ -16736,7 +16735,7 @@
       </c>
       <c r="AD98" s="5"/>
     </row>
-    <row r="99" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
         <v>737</v>
       </c>
@@ -16779,7 +16778,7 @@
       </c>
       <c r="AD99" s="5"/>
     </row>
-    <row r="100" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="15" t="s">
         <v>738</v>
       </c>
@@ -16822,7 +16821,7 @@
       </c>
       <c r="AD100" s="5"/>
     </row>
-    <row r="101" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="15" t="s">
         <v>739</v>
       </c>
@@ -16867,7 +16866,7 @@
       </c>
       <c r="AD101" s="5"/>
     </row>
-    <row r="102" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="15" t="s">
         <v>740</v>
       </c>
@@ -16912,7 +16911,7 @@
       </c>
       <c r="AD102" s="5"/>
     </row>
-    <row r="103" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="15" t="s">
         <v>741</v>
       </c>
@@ -16955,7 +16954,7 @@
       </c>
       <c r="AD103" s="5"/>
     </row>
-    <row r="104" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="15" t="s">
         <v>742</v>
       </c>
@@ -16998,7 +16997,7 @@
       </c>
       <c r="AD104" s="5"/>
     </row>
-    <row r="105" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="15" t="s">
         <v>743</v>
       </c>
@@ -17043,7 +17042,7 @@
       </c>
       <c r="AD105" s="5"/>
     </row>
-    <row r="106" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="15" t="s">
         <v>744</v>
       </c>
@@ -17086,7 +17085,7 @@
       </c>
       <c r="AD106" s="5"/>
     </row>
-    <row r="107" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="15" t="s">
         <v>745</v>
       </c>
@@ -17131,7 +17130,7 @@
       </c>
       <c r="AD107" s="5"/>
     </row>
-    <row r="108" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="15" t="s">
         <v>746</v>
       </c>
@@ -17174,7 +17173,7 @@
       </c>
       <c r="AD108" s="5"/>
     </row>
-    <row r="109" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="15" t="s">
         <v>747</v>
       </c>
@@ -17217,7 +17216,7 @@
       </c>
       <c r="AD109" s="5"/>
     </row>
-    <row r="110" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="15" t="s">
         <v>748</v>
       </c>
@@ -17260,7 +17259,7 @@
       </c>
       <c r="AD110" s="5"/>
     </row>
-    <row r="111" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="15" t="s">
         <v>749</v>
       </c>
@@ -17303,7 +17302,7 @@
       </c>
       <c r="AD111" s="5"/>
     </row>
-    <row r="112" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="15" t="s">
         <v>750</v>
       </c>
@@ -17346,7 +17345,7 @@
       </c>
       <c r="AD112" s="5"/>
     </row>
-    <row r="113" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="15" t="s">
         <v>751</v>
       </c>
@@ -17389,7 +17388,7 @@
       </c>
       <c r="AD113" s="5"/>
     </row>
-    <row r="114" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="15" t="s">
         <v>752</v>
       </c>
@@ -17434,7 +17433,7 @@
       </c>
       <c r="AD114" s="5"/>
     </row>
-    <row r="115" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="15" t="s">
         <v>753</v>
       </c>
@@ -17479,7 +17478,7 @@
       </c>
       <c r="AD115" s="5"/>
     </row>
-    <row r="116" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="15" t="s">
         <v>754</v>
       </c>
@@ -17522,7 +17521,7 @@
       </c>
       <c r="AD116" s="5"/>
     </row>
-    <row r="117" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="15" t="s">
         <v>755</v>
       </c>
@@ -17565,7 +17564,7 @@
       </c>
       <c r="AD117" s="5"/>
     </row>
-    <row r="118" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="15" t="s">
         <v>756</v>
       </c>
@@ -17608,7 +17607,7 @@
       </c>
       <c r="AD118" s="5"/>
     </row>
-    <row r="119" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="15" t="s">
         <v>757</v>
       </c>
@@ -17653,7 +17652,7 @@
       </c>
       <c r="AD119" s="5"/>
     </row>
-    <row r="120" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="15" t="s">
         <v>758</v>
       </c>
@@ -17698,7 +17697,7 @@
       </c>
       <c r="AD120" s="5"/>
     </row>
-    <row r="121" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="15" t="s">
         <v>759</v>
       </c>
@@ -17741,7 +17740,7 @@
       </c>
       <c r="AD121" s="5"/>
     </row>
-    <row r="122" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="15" t="s">
         <v>760</v>
       </c>
@@ -17786,7 +17785,7 @@
       </c>
       <c r="AD122" s="5"/>
     </row>
-    <row r="123" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="15" t="s">
         <v>761</v>
       </c>
@@ -17831,7 +17830,7 @@
       </c>
       <c r="AD123" s="5"/>
     </row>
-    <row r="124" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="15" t="s">
         <v>762</v>
       </c>
@@ -17874,7 +17873,7 @@
       </c>
       <c r="AD124" s="5"/>
     </row>
-    <row r="125" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="15" t="s">
         <v>763</v>
       </c>
@@ -17919,7 +17918,7 @@
       </c>
       <c r="AD125" s="5"/>
     </row>
-    <row r="126" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="15" t="s">
         <v>764</v>
       </c>
@@ -17964,7 +17963,7 @@
       </c>
       <c r="AD126" s="5"/>
     </row>
-    <row r="127" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="15" t="s">
         <v>765</v>
       </c>
@@ -18009,7 +18008,7 @@
       </c>
       <c r="AD127" s="5"/>
     </row>
-    <row r="128" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="15" t="s">
         <v>766</v>
       </c>
@@ -18052,7 +18051,7 @@
       </c>
       <c r="AD128" s="5"/>
     </row>
-    <row r="129" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="15" t="s">
         <v>767</v>
       </c>
@@ -18095,7 +18094,7 @@
       </c>
       <c r="AD129" s="5"/>
     </row>
-    <row r="130" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="15" t="s">
         <v>768</v>
       </c>
@@ -18138,7 +18137,7 @@
       </c>
       <c r="AD130" s="5"/>
     </row>
-    <row r="131" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="15" t="s">
         <v>769</v>
       </c>
@@ -18181,7 +18180,7 @@
       </c>
       <c r="AD131" s="5"/>
     </row>
-    <row r="132" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="15" t="s">
         <v>770</v>
       </c>
@@ -18226,7 +18225,7 @@
       </c>
       <c r="AD132" s="5"/>
     </row>
-    <row r="133" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="15" t="s">
         <v>771</v>
       </c>
@@ -18271,7 +18270,7 @@
       </c>
       <c r="AD133" s="5"/>
     </row>
-    <row r="134" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="15" t="s">
         <v>772</v>
       </c>
@@ -18316,7 +18315,7 @@
       </c>
       <c r="AD134" s="5"/>
     </row>
-    <row r="135" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="15" t="s">
         <v>773</v>
       </c>
@@ -18361,7 +18360,7 @@
       </c>
       <c r="AD135" s="5"/>
     </row>
-    <row r="136" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="15" t="s">
         <v>774</v>
       </c>
@@ -18404,7 +18403,7 @@
       </c>
       <c r="AD136" s="5"/>
     </row>
-    <row r="137" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="15" t="s">
         <v>775</v>
       </c>
@@ -18449,7 +18448,7 @@
       </c>
       <c r="AD137" s="5"/>
     </row>
-    <row r="138" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="15" t="s">
         <v>776</v>
       </c>
@@ -18492,7 +18491,7 @@
       </c>
       <c r="AD138" s="5"/>
     </row>
-    <row r="139" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="15" t="s">
         <v>777</v>
       </c>
@@ -18535,7 +18534,7 @@
       </c>
       <c r="AD139" s="5"/>
     </row>
-    <row r="140" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="15" t="s">
         <v>778</v>
       </c>
@@ -18578,7 +18577,7 @@
       </c>
       <c r="AD140" s="5"/>
     </row>
-    <row r="141" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="15" t="s">
         <v>779</v>
       </c>
@@ -18621,7 +18620,7 @@
       </c>
       <c r="AD141" s="5"/>
     </row>
-    <row r="142" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="15" t="s">
         <v>780</v>
       </c>
@@ -18664,7 +18663,7 @@
       </c>
       <c r="AD142" s="5"/>
     </row>
-    <row r="143" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="15" t="s">
         <v>781</v>
       </c>
@@ -18715,7 +18714,7 @@
       </c>
       <c r="AD143" s="5"/>
     </row>
-    <row r="144" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="15" t="s">
         <v>782</v>
       </c>
@@ -18758,7 +18757,7 @@
       </c>
       <c r="AD144" s="5"/>
     </row>
-    <row r="145" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="15" t="s">
         <v>783</v>
       </c>
@@ -18801,7 +18800,7 @@
       </c>
       <c r="AD145" s="5"/>
     </row>
-    <row r="146" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="155" t="s">
         <v>784</v>
       </c>
@@ -18864,7 +18863,7 @@
       </c>
       <c r="AD146" s="5"/>
     </row>
-    <row r="147" spans="1:30" s="69" customFormat="1" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:30" s="69" customFormat="1" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="15" t="s">
         <v>785</v>
       </c>
@@ -18918,7 +18917,7 @@
       </c>
       <c r="AD147" s="5"/>
     </row>
-    <row r="148" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="15" t="s">
         <v>786</v>
       </c>
@@ -18961,7 +18960,7 @@
       </c>
       <c r="AD148" s="5"/>
     </row>
-    <row r="149" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="15" t="s">
         <v>787</v>
       </c>
@@ -19006,7 +19005,7 @@
       </c>
       <c r="AD149" s="5"/>
     </row>
-    <row r="150" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="15" t="s">
         <v>788</v>
       </c>
@@ -19051,7 +19050,7 @@
       </c>
       <c r="AD150" s="5"/>
     </row>
-    <row r="151" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="15" t="s">
         <v>789</v>
       </c>
@@ -19096,7 +19095,7 @@
       </c>
       <c r="AD151" s="5"/>
     </row>
-    <row r="152" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="15" t="s">
         <v>790</v>
       </c>
@@ -19145,7 +19144,7 @@
       </c>
       <c r="AD152" s="5"/>
     </row>
-    <row r="153" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="15" t="s">
         <v>791</v>
       </c>
@@ -19188,7 +19187,7 @@
       </c>
       <c r="AD153" s="5"/>
     </row>
-    <row r="154" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="15" t="s">
         <v>792</v>
       </c>
@@ -19239,7 +19238,7 @@
       </c>
       <c r="AD154" s="5"/>
     </row>
-    <row r="155" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="15" t="s">
         <v>793</v>
       </c>
@@ -19282,7 +19281,7 @@
       </c>
       <c r="AD155" s="5"/>
     </row>
-    <row r="156" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="15" t="s">
         <v>794</v>
       </c>
@@ -19325,7 +19324,7 @@
       </c>
       <c r="AD156" s="5"/>
     </row>
-    <row r="157" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="15" t="s">
         <v>795</v>
       </c>
@@ -19368,7 +19367,7 @@
       </c>
       <c r="AD157" s="5"/>
     </row>
-    <row r="158" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="15" t="s">
         <v>796</v>
       </c>
@@ -19419,7 +19418,7 @@
       </c>
       <c r="AD158" s="5"/>
     </row>
-    <row r="159" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="15" t="s">
         <v>797</v>
       </c>
@@ -19464,7 +19463,7 @@
       </c>
       <c r="AD159" s="5"/>
     </row>
-    <row r="160" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="15" t="s">
         <v>798</v>
       </c>
@@ -19507,7 +19506,7 @@
       </c>
       <c r="AD160" s="5"/>
     </row>
-    <row r="161" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="15" t="s">
         <v>799</v>
       </c>
@@ -19552,7 +19551,7 @@
       </c>
       <c r="AD161" s="5"/>
     </row>
-    <row r="162" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="15" t="s">
         <v>800</v>
       </c>
@@ -19597,7 +19596,7 @@
       </c>
       <c r="AD162" s="5"/>
     </row>
-    <row r="163" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="15" t="s">
         <v>801</v>
       </c>
@@ -19642,7 +19641,7 @@
       </c>
       <c r="AD163" s="5"/>
     </row>
-    <row r="164" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="15" t="s">
         <v>802</v>
       </c>
@@ -19685,7 +19684,7 @@
       </c>
       <c r="AD164" s="5"/>
     </row>
-    <row r="165" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="15" t="s">
         <v>803</v>
       </c>
@@ -19730,7 +19729,7 @@
       </c>
       <c r="AD165" s="5"/>
     </row>
-    <row r="166" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="15" t="s">
         <v>804</v>
       </c>
@@ -19773,7 +19772,7 @@
       </c>
       <c r="AD166" s="5"/>
     </row>
-    <row r="167" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="15" t="s">
         <v>805</v>
       </c>
@@ -19816,7 +19815,7 @@
       </c>
       <c r="AD167" s="5"/>
     </row>
-    <row r="168" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="15" t="s">
         <v>806</v>
       </c>
@@ -19859,7 +19858,7 @@
       </c>
       <c r="AD168" s="5"/>
     </row>
-    <row r="169" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="15" t="s">
         <v>807</v>
       </c>
@@ -19902,7 +19901,7 @@
       </c>
       <c r="AD169" s="5"/>
     </row>
-    <row r="170" spans="1:30" s="69" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:30" s="69" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="155" t="s">
         <v>808</v>
       </c>
@@ -19974,7 +19973,7 @@
       </c>
       <c r="AD170" s="145"/>
     </row>
-    <row r="171" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="15" t="s">
         <v>809</v>
       </c>
@@ -20017,7 +20016,7 @@
       </c>
       <c r="AD171" s="5"/>
     </row>
-    <row r="172" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="15" t="s">
         <v>810</v>
       </c>
@@ -20060,7 +20059,7 @@
       </c>
       <c r="AD172" s="5"/>
     </row>
-    <row r="173" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="15" t="s">
         <v>811</v>
       </c>
@@ -20105,7 +20104,7 @@
       </c>
       <c r="AD173" s="5"/>
     </row>
-    <row r="174" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="15" t="s">
         <v>812</v>
       </c>
@@ -20150,7 +20149,7 @@
       </c>
       <c r="AD174" s="5"/>
     </row>
-    <row r="175" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="15" t="s">
         <v>813</v>
       </c>
@@ -20195,7 +20194,7 @@
       </c>
       <c r="AD175" s="5"/>
     </row>
-    <row r="176" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="15" t="s">
         <v>814</v>
       </c>
@@ -20238,7 +20237,7 @@
       </c>
       <c r="AD176" s="5"/>
     </row>
-    <row r="177" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="15" t="s">
         <v>815</v>
       </c>
@@ -20281,7 +20280,7 @@
       </c>
       <c r="AD177" s="5"/>
     </row>
-    <row r="178" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="15" t="s">
         <v>816</v>
       </c>
@@ -20326,7 +20325,7 @@
       </c>
       <c r="AD178" s="5"/>
     </row>
-    <row r="179" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="15" t="s">
         <v>817</v>
       </c>
@@ -20369,7 +20368,7 @@
       </c>
       <c r="AD179" s="5"/>
     </row>
-    <row r="180" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="15" t="s">
         <v>818</v>
       </c>
@@ -20414,7 +20413,7 @@
       </c>
       <c r="AD180" s="5"/>
     </row>
-    <row r="181" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="15" t="s">
         <v>819</v>
       </c>
@@ -20459,7 +20458,7 @@
       </c>
       <c r="AD181" s="5"/>
     </row>
-    <row r="182" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="15" t="s">
         <v>820</v>
       </c>
@@ -20504,7 +20503,7 @@
       </c>
       <c r="AD182" s="5"/>
     </row>
-    <row r="183" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="15" t="s">
         <v>821</v>
       </c>
@@ -20549,7 +20548,7 @@
       </c>
       <c r="AD183" s="5"/>
     </row>
-    <row r="184" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="15" t="s">
         <v>822</v>
       </c>
@@ -20594,7 +20593,7 @@
       </c>
       <c r="AD184" s="5"/>
     </row>
-    <row r="185" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="15" t="s">
         <v>823</v>
       </c>
@@ -20639,7 +20638,7 @@
       </c>
       <c r="AD185" s="5"/>
     </row>
-    <row r="186" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="15" t="s">
         <v>824</v>
       </c>
@@ -20682,7 +20681,7 @@
       </c>
       <c r="AD186" s="5"/>
     </row>
-    <row r="187" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="15" t="s">
         <v>825</v>
       </c>
@@ -20727,7 +20726,7 @@
       </c>
       <c r="AD187" s="5"/>
     </row>
-    <row r="188" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="15" t="s">
         <v>826</v>
       </c>
@@ -20772,7 +20771,7 @@
       </c>
       <c r="AD188" s="5"/>
     </row>
-    <row r="189" spans="1:30" s="69" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:30" s="69" customFormat="1" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="15" t="s">
         <v>827</v>
       </c>
@@ -20823,7 +20822,7 @@
       </c>
       <c r="AD189" s="5"/>
     </row>
-    <row r="190" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="15" t="s">
         <v>828</v>
       </c>
@@ -20868,7 +20867,7 @@
       </c>
       <c r="AD190" s="5"/>
     </row>
-    <row r="191" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="15" t="s">
         <v>829</v>
       </c>
@@ -20913,7 +20912,7 @@
       </c>
       <c r="AD191" s="5"/>
     </row>
-    <row r="192" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="15" t="s">
         <v>830</v>
       </c>
@@ -20958,7 +20957,7 @@
       </c>
       <c r="AD192" s="5"/>
     </row>
-    <row r="193" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="15" t="s">
         <v>831</v>
       </c>
@@ -20997,7 +20996,7 @@
       </c>
       <c r="AD193" s="5"/>
     </row>
-    <row r="194" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="15" t="s">
         <v>832</v>
       </c>
@@ -21036,7 +21035,7 @@
       </c>
       <c r="AD194" s="5"/>
     </row>
-    <row r="195" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="15" t="s">
         <v>833</v>
       </c>
@@ -21075,7 +21074,7 @@
       </c>
       <c r="AD195" s="5"/>
     </row>
-    <row r="196" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="15" t="s">
         <v>834</v>
       </c>
@@ -21126,7 +21125,7 @@
       </c>
       <c r="AD196" s="5"/>
     </row>
-    <row r="197" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="15" t="s">
         <v>835</v>
       </c>
@@ -21177,7 +21176,7 @@
       </c>
       <c r="AD197" s="5"/>
     </row>
-    <row r="198" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="15" t="s">
         <v>836</v>
       </c>
@@ -21228,7 +21227,7 @@
       </c>
       <c r="AD198" s="5"/>
     </row>
-    <row r="199" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="15" t="s">
         <v>837</v>
       </c>
@@ -21273,7 +21272,7 @@
       </c>
       <c r="AD199" s="5"/>
     </row>
-    <row r="200" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="15" t="s">
         <v>838</v>
       </c>
@@ -21316,7 +21315,7 @@
       </c>
       <c r="AD200" s="5"/>
     </row>
-    <row r="201" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="15" t="s">
         <v>839</v>
       </c>
@@ -21361,7 +21360,7 @@
       </c>
       <c r="AD201" s="5"/>
     </row>
-    <row r="202" spans="1:30" s="69" customFormat="1" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:30" s="69" customFormat="1" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="15" t="s">
         <v>840</v>
       </c>
@@ -21412,7 +21411,7 @@
       </c>
       <c r="AD202" s="5"/>
     </row>
-    <row r="203" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="15" t="s">
         <v>841</v>
       </c>
@@ -21457,7 +21456,7 @@
       </c>
       <c r="AD203" s="5"/>
     </row>
-    <row r="204" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="15" t="s">
         <v>842</v>
       </c>
@@ -21502,7 +21501,7 @@
       </c>
       <c r="AD204" s="5"/>
     </row>
-    <row r="205" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="15" t="s">
         <v>843</v>
       </c>
@@ -21547,7 +21546,7 @@
       </c>
       <c r="AD205" s="5"/>
     </row>
-    <row r="206" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="15" t="s">
         <v>844</v>
       </c>
@@ -21590,7 +21589,7 @@
       </c>
       <c r="AD206" s="5"/>
     </row>
-    <row r="207" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="15" t="s">
         <v>845</v>
       </c>
@@ -21635,7 +21634,7 @@
       </c>
       <c r="AD207" s="5"/>
     </row>
-    <row r="208" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="15" t="s">
         <v>846</v>
       </c>
@@ -21680,7 +21679,7 @@
       </c>
       <c r="AD208" s="5"/>
     </row>
-    <row r="209" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="15" t="s">
         <v>847</v>
       </c>
@@ -21725,7 +21724,7 @@
       </c>
       <c r="AD209" s="5"/>
     </row>
-    <row r="210" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="15" t="s">
         <v>848</v>
       </c>
@@ -21776,7 +21775,7 @@
       </c>
       <c r="AD210" s="5"/>
     </row>
-    <row r="211" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="15" t="s">
         <v>849</v>
       </c>
@@ -21819,7 +21818,7 @@
       </c>
       <c r="AD211" s="5"/>
     </row>
-    <row r="212" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="15" t="s">
         <v>850</v>
       </c>
@@ -21866,7 +21865,7 @@
       </c>
       <c r="AD212" s="5"/>
     </row>
-    <row r="213" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:30" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="15" t="s">
         <v>851</v>
       </c>
@@ -21917,7 +21916,7 @@
       </c>
       <c r="AD213" s="5"/>
     </row>
-    <row r="214" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="15" t="s">
         <v>852</v>
       </c>
@@ -21974,7 +21973,7 @@
       </c>
       <c r="AD214" s="1"/>
     </row>
-    <row r="215" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="15" t="s">
         <v>853</v>
       </c>
@@ -22023,7 +22022,7 @@
       </c>
       <c r="AD215" s="1"/>
     </row>
-    <row r="216" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="15" t="s">
         <v>1215</v>
       </c>
@@ -22072,7 +22071,7 @@
       </c>
       <c r="AD216" s="1"/>
     </row>
-    <row r="217" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="15" t="s">
         <v>1216</v>
       </c>
@@ -22121,7 +22120,7 @@
       </c>
       <c r="AD217" s="1"/>
     </row>
-    <row r="218" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="15" t="s">
         <v>1217</v>
       </c>
@@ -22170,7 +22169,7 @@
       </c>
       <c r="AD218" s="1"/>
     </row>
-    <row r="219" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="15" t="s">
         <v>1218</v>
       </c>
@@ -22219,7 +22218,7 @@
       </c>
       <c r="AD219" s="1"/>
     </row>
-    <row r="220" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="15" t="s">
         <v>1219</v>
       </c>
@@ -22268,7 +22267,7 @@
       </c>
       <c r="AD220" s="1"/>
     </row>
-    <row r="221" spans="1:30" ht="28" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" s="15" t="s">
         <v>1223</v>
       </c>
@@ -22317,7 +22316,7 @@
       </c>
       <c r="AD221" s="1"/>
     </row>
-    <row r="222" spans="1:30" ht="42" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="15" t="s">
         <v>1224</v>
       </c>
@@ -22366,7 +22365,7 @@
       </c>
       <c r="AD222" s="1"/>
     </row>
-    <row r="223" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="15" t="s">
         <v>1225</v>
       </c>
@@ -22427,7 +22426,7 @@
       </c>
       <c r="AD223" s="1"/>
     </row>
-    <row r="224" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="15" t="s">
         <v>1226</v>
       </c>
@@ -22476,7 +22475,7 @@
       </c>
       <c r="AD224" s="1"/>
     </row>
-    <row r="225" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="15" t="s">
         <v>1227</v>
       </c>
@@ -22529,7 +22528,7 @@
       </c>
       <c r="AD225" s="1"/>
     </row>
-    <row r="226" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="15" t="s">
         <v>1228</v>
       </c>
@@ -22574,7 +22573,7 @@
       </c>
       <c r="AD226" s="1"/>
     </row>
-    <row r="227" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="15" t="s">
         <v>1229</v>
       </c>
@@ -22619,7 +22618,7 @@
       </c>
       <c r="AD227" s="1"/>
     </row>
-    <row r="228" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="15" t="s">
         <v>1230</v>
       </c>
@@ -22666,7 +22665,7 @@
       </c>
       <c r="AD228" s="1"/>
     </row>
-    <row r="229" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="15" t="s">
         <v>1231</v>
       </c>
@@ -22711,7 +22710,7 @@
       </c>
       <c r="AD229" s="1"/>
     </row>
-    <row r="230" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="15" t="s">
         <v>1232</v>
       </c>
@@ -22754,7 +22753,7 @@
       </c>
       <c r="AD230" s="1"/>
     </row>
-    <row r="231" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="15" t="s">
         <v>1246</v>
       </c>
@@ -22801,7 +22800,7 @@
       </c>
       <c r="AD231" s="1"/>
     </row>
-    <row r="232" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="15" t="s">
         <v>1247</v>
       </c>
@@ -22846,7 +22845,7 @@
       </c>
       <c r="AD232" s="1"/>
     </row>
-    <row r="233" spans="1:30" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:30" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="15" t="s">
         <v>1248</v>
       </c>
@@ -22891,7 +22890,7 @@
       </c>
       <c r="AD233" s="1"/>
     </row>
-    <row r="234" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="200" t="s">
         <v>1323</v>
       </c>
@@ -22933,7 +22932,7 @@
       <c r="AC234" s="1"/>
       <c r="AD234" s="1"/>
     </row>
-    <row r="235" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="200" t="s">
         <v>1324</v>
       </c>
@@ -22975,7 +22974,7 @@
       <c r="AC235" s="1"/>
       <c r="AD235" s="1"/>
     </row>
-    <row r="236" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="200" t="s">
         <v>1325</v>
       </c>
@@ -23017,7 +23016,7 @@
       <c r="AC236" s="1"/>
       <c r="AD236" s="1"/>
     </row>
-    <row r="237" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="200" t="s">
         <v>1326</v>
       </c>
@@ -23059,7 +23058,7 @@
       <c r="AC237" s="1"/>
       <c r="AD237" s="1"/>
     </row>
-    <row r="238" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="200" t="s">
         <v>1327</v>
       </c>
@@ -23103,7 +23102,7 @@
       <c r="AC238" s="1"/>
       <c r="AD238" s="1"/>
     </row>
-    <row r="239" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="200" t="s">
         <v>1328</v>
       </c>
@@ -23145,7 +23144,7 @@
       <c r="AC239" s="1"/>
       <c r="AD239" s="1"/>
     </row>
-    <row r="240" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="200" t="s">
         <v>1329</v>
       </c>
@@ -23185,7 +23184,7 @@
       <c r="AC240" s="1"/>
       <c r="AD240" s="1"/>
     </row>
-    <row r="241" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="200" t="s">
         <v>1330</v>
       </c>
@@ -23227,7 +23226,7 @@
       <c r="AC241" s="1"/>
       <c r="AD241" s="1"/>
     </row>
-    <row r="242" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="200" t="s">
         <v>1331</v>
       </c>
@@ -23269,7 +23268,7 @@
       <c r="AC242" s="1"/>
       <c r="AD242" s="1"/>
     </row>
-    <row r="243" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="200" t="s">
         <v>1332</v>
       </c>
@@ -23313,7 +23312,7 @@
       <c r="AC243" s="1"/>
       <c r="AD243" s="1"/>
     </row>
-    <row r="244" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="200" t="s">
         <v>1333</v>
       </c>
@@ -23355,7 +23354,7 @@
       <c r="AC244" s="1"/>
       <c r="AD244" s="1"/>
     </row>
-    <row r="245" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="200" t="s">
         <v>1334</v>
       </c>
@@ -23399,7 +23398,7 @@
       <c r="AC245" s="1"/>
       <c r="AD245" s="1"/>
     </row>
-    <row r="246" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="200" t="s">
         <v>1335</v>
       </c>
@@ -23433,7 +23432,7 @@
       <c r="AC246" s="1"/>
       <c r="AD246" s="1"/>
     </row>
-    <row r="247" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="200" t="s">
         <v>1336</v>
       </c>
@@ -23467,7 +23466,7 @@
       <c r="AC247" s="1"/>
       <c r="AD247" s="1"/>
     </row>
-    <row r="248" spans="1:30" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:30" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="200" t="s">
         <v>1337</v>
       </c>
@@ -23501,7 +23500,7 @@
       <c r="AC248" s="1"/>
       <c r="AD248" s="1"/>
     </row>
-    <row r="249" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B249" s="1"/>
       <c r="C249" s="90"/>
       <c r="D249" s="1"/>
@@ -23532,7 +23531,7 @@
       <c r="AC249" s="1"/>
       <c r="AD249" s="1"/>
     </row>
-    <row r="250" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B250" s="1"/>
       <c r="C250" s="90"/>
       <c r="D250" s="1"/>
@@ -23563,7 +23562,7 @@
       <c r="AC250" s="1"/>
       <c r="AD250" s="1"/>
     </row>
-    <row r="251" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B251" s="1"/>
       <c r="C251" s="90"/>
       <c r="D251" s="1"/>
@@ -23594,7 +23593,7 @@
       <c r="AC251" s="1"/>
       <c r="AD251" s="1"/>
     </row>
-    <row r="252" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B252" s="1"/>
       <c r="C252" s="90"/>
       <c r="D252" s="1"/>
@@ -23625,7 +23624,7 @@
       <c r="AC252" s="1"/>
       <c r="AD252" s="1"/>
     </row>
-    <row r="253" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B253" s="1"/>
       <c r="C253" s="90"/>
       <c r="D253" s="1"/>
@@ -23656,7 +23655,7 @@
       <c r="AC253" s="1"/>
       <c r="AD253" s="1"/>
     </row>
-    <row r="254" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B254" s="1"/>
       <c r="C254" s="90"/>
       <c r="D254" s="1"/>
@@ -23687,7 +23686,7 @@
       <c r="AC254" s="1"/>
       <c r="AD254" s="1"/>
     </row>
-    <row r="255" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B255" s="1"/>
       <c r="C255" s="90"/>
       <c r="D255" s="1"/>
@@ -23718,7 +23717,7 @@
       <c r="AC255" s="1"/>
       <c r="AD255" s="1"/>
     </row>
-    <row r="256" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B256" s="1"/>
       <c r="C256" s="90"/>
       <c r="D256" s="1"/>
@@ -23749,7 +23748,7 @@
       <c r="AC256" s="1"/>
       <c r="AD256" s="1"/>
     </row>
-    <row r="257" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B257" s="1"/>
       <c r="C257" s="90"/>
       <c r="D257" s="1"/>
@@ -23780,7 +23779,7 @@
       <c r="AC257" s="1"/>
       <c r="AD257" s="1"/>
     </row>
-    <row r="258" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B258" s="1"/>
       <c r="C258" s="90"/>
       <c r="D258" s="1"/>
@@ -23811,7 +23810,7 @@
       <c r="AC258" s="1"/>
       <c r="AD258" s="1"/>
     </row>
-    <row r="259" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B259" s="1"/>
       <c r="C259" s="90"/>
       <c r="D259" s="1"/>
@@ -23842,7 +23841,7 @@
       <c r="AC259" s="1"/>
       <c r="AD259" s="1"/>
     </row>
-    <row r="260" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B260" s="1"/>
       <c r="C260" s="90"/>
       <c r="D260" s="1"/>
@@ -23873,7 +23872,7 @@
       <c r="AC260" s="1"/>
       <c r="AD260" s="1"/>
     </row>
-    <row r="261" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B261" s="1"/>
       <c r="C261" s="90"/>
       <c r="D261" s="1"/>
@@ -23904,7 +23903,7 @@
       <c r="AC261" s="1"/>
       <c r="AD261" s="1"/>
     </row>
-    <row r="262" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B262" s="1"/>
       <c r="C262" s="90"/>
       <c r="D262" s="1"/>
@@ -23935,7 +23934,7 @@
       <c r="AC262" s="1"/>
       <c r="AD262" s="1"/>
     </row>
-    <row r="263" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B263" s="1"/>
       <c r="C263" s="90"/>
       <c r="D263" s="1"/>
@@ -23966,7 +23965,7 @@
       <c r="AC263" s="1"/>
       <c r="AD263" s="1"/>
     </row>
-    <row r="264" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B264" s="1"/>
       <c r="C264" s="90"/>
       <c r="D264" s="1"/>
@@ -23997,7 +23996,7 @@
       <c r="AC264" s="1"/>
       <c r="AD264" s="1"/>
     </row>
-    <row r="265" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B265" s="1"/>
       <c r="C265" s="90"/>
       <c r="D265" s="1"/>
@@ -24028,7 +24027,7 @@
       <c r="AC265" s="1"/>
       <c r="AD265" s="1"/>
     </row>
-    <row r="266" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B266" s="1"/>
       <c r="C266" s="90"/>
       <c r="D266" s="1"/>
@@ -24059,7 +24058,7 @@
       <c r="AC266" s="1"/>
       <c r="AD266" s="1"/>
     </row>
-    <row r="267" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B267" s="1"/>
       <c r="C267" s="90"/>
       <c r="D267" s="1"/>
@@ -24090,7 +24089,7 @@
       <c r="AC267" s="1"/>
       <c r="AD267" s="1"/>
     </row>
-    <row r="268" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B268" s="1"/>
       <c r="C268" s="90"/>
       <c r="D268" s="1"/>
@@ -24121,7 +24120,7 @@
       <c r="AC268" s="1"/>
       <c r="AD268" s="1"/>
     </row>
-    <row r="269" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B269" s="1"/>
       <c r="C269" s="90"/>
       <c r="D269" s="1"/>
@@ -24152,7 +24151,7 @@
       <c r="AC269" s="1"/>
       <c r="AD269" s="1"/>
     </row>
-    <row r="270" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B270" s="1"/>
       <c r="C270" s="90"/>
       <c r="D270" s="1"/>
@@ -24183,7 +24182,7 @@
       <c r="AC270" s="1"/>
       <c r="AD270" s="1"/>
     </row>
-    <row r="271" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B271" s="1"/>
       <c r="C271" s="90"/>
       <c r="D271" s="1"/>
@@ -24214,7 +24213,7 @@
       <c r="AC271" s="1"/>
       <c r="AD271" s="1"/>
     </row>
-    <row r="272" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B272" s="1"/>
       <c r="C272" s="90"/>
       <c r="D272" s="1"/>
@@ -24245,7 +24244,7 @@
       <c r="AC272" s="1"/>
       <c r="AD272" s="1"/>
     </row>
-    <row r="273" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B273" s="1"/>
       <c r="C273" s="90"/>
       <c r="D273" s="1"/>
@@ -24276,7 +24275,7 @@
       <c r="AC273" s="1"/>
       <c r="AD273" s="1"/>
     </row>
-    <row r="274" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B274" s="1"/>
       <c r="C274" s="90"/>
       <c r="D274" s="1"/>
@@ -24307,7 +24306,7 @@
       <c r="AC274" s="1"/>
       <c r="AD274" s="1"/>
     </row>
-    <row r="275" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B275" s="1"/>
       <c r="C275" s="90"/>
       <c r="D275" s="1"/>
@@ -24338,7 +24337,7 @@
       <c r="AC275" s="1"/>
       <c r="AD275" s="1"/>
     </row>
-    <row r="276" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B276" s="1"/>
       <c r="C276" s="90"/>
       <c r="D276" s="1"/>
@@ -24369,7 +24368,7 @@
       <c r="AC276" s="1"/>
       <c r="AD276" s="1"/>
     </row>
-    <row r="277" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
@@ -24400,7 +24399,7 @@
       <c r="AC277" s="1"/>
       <c r="AD277" s="1"/>
     </row>
-    <row r="278" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
@@ -24431,7 +24430,7 @@
       <c r="AC278" s="1"/>
       <c r="AD278" s="1"/>
     </row>
-    <row r="279" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
@@ -24462,7 +24461,7 @@
       <c r="AC279" s="1"/>
       <c r="AD279" s="1"/>
     </row>
-    <row r="280" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
@@ -24493,7 +24492,7 @@
       <c r="AC280" s="1"/>
       <c r="AD280" s="1"/>
     </row>
-    <row r="281" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
@@ -24524,7 +24523,7 @@
       <c r="AC281" s="1"/>
       <c r="AD281" s="1"/>
     </row>
-    <row r="282" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
@@ -24555,7 +24554,7 @@
       <c r="AC282" s="1"/>
       <c r="AD282" s="1"/>
     </row>
-    <row r="283" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
@@ -24586,7 +24585,7 @@
       <c r="AC283" s="1"/>
       <c r="AD283" s="1"/>
     </row>
-    <row r="284" spans="2:30" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
@@ -24619,13 +24618,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="A2:A3"/>
@@ -24637,6 +24629,13 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AC3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24649,25 +24648,25 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:AD41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32.1796875" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" customWidth="1"/>
-    <col min="6" max="6" width="29.81640625" customWidth="1"/>
-    <col min="8" max="8" width="35.1796875" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" customWidth="1"/>
-    <col min="10" max="10" width="14.54296875" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" customWidth="1"/>
-    <col min="12" max="13" width="9.81640625" style="179" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="8" max="8" width="35.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="13" width="9.85546875" style="179" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="L1"/>
       <c r="M1"/>
     </row>
-    <row r="2" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="224" t="s">
         <v>0</v>
       </c>
@@ -24735,7 +24734,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="224"/>
       <c r="B3" s="224"/>
       <c r="C3" s="16" t="s">
@@ -24803,7 +24802,7 @@
       <c r="AC3" s="224"/>
       <c r="AD3" s="224"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>65</v>
       </c>
@@ -24846,7 +24845,7 @@
       </c>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>66</v>
       </c>
@@ -24887,7 +24886,7 @@
       </c>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>67</v>
       </c>
@@ -24928,7 +24927,7 @@
       </c>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>68</v>
       </c>
@@ -24977,7 +24976,7 @@
       </c>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>69</v>
       </c>
@@ -25026,7 +25025,7 @@
       </c>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>70</v>
       </c>
@@ -25075,7 +25074,7 @@
       </c>
       <c r="AD9" s="1"/>
     </row>
-    <row r="10" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>71</v>
       </c>
@@ -25124,7 +25123,7 @@
       </c>
       <c r="AD10" s="1"/>
     </row>
-    <row r="11" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>72</v>
       </c>
@@ -25167,7 +25166,7 @@
       </c>
       <c r="AD11" s="1"/>
     </row>
-    <row r="12" spans="1:30" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" ht="36" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>73</v>
       </c>
@@ -25216,7 +25215,7 @@
       </c>
       <c r="AD12" s="1"/>
     </row>
-    <row r="13" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>74</v>
       </c>
@@ -25265,7 +25264,7 @@
       </c>
       <c r="AD13" s="1"/>
     </row>
-    <row r="14" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>75</v>
       </c>
@@ -25314,7 +25313,7 @@
       </c>
       <c r="AD14" s="1"/>
     </row>
-    <row r="15" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>76</v>
       </c>
@@ -25363,7 +25362,7 @@
       </c>
       <c r="AD15" s="1"/>
     </row>
-    <row r="16" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>77</v>
       </c>
@@ -25412,7 +25411,7 @@
       </c>
       <c r="AD16" s="1"/>
     </row>
-    <row r="17" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>78</v>
       </c>
@@ -25461,7 +25460,7 @@
       </c>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>79</v>
       </c>
@@ -25504,7 +25503,7 @@
       </c>
       <c r="AD18" s="1"/>
     </row>
-    <row r="19" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>854</v>
       </c>
@@ -25553,7 +25552,7 @@
       </c>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>855</v>
       </c>
@@ -25602,7 +25601,7 @@
       </c>
       <c r="AD20" s="1"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>856</v>
       </c>
@@ -25651,7 +25650,7 @@
       </c>
       <c r="AD21" s="1"/>
     </row>
-    <row r="22" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>857</v>
       </c>
@@ -25700,7 +25699,7 @@
       </c>
       <c r="AD22" s="1"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>858</v>
       </c>
@@ -25749,7 +25748,7 @@
       </c>
       <c r="AD23" s="1"/>
     </row>
-    <row r="24" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>859</v>
       </c>
@@ -25798,7 +25797,7 @@
       </c>
       <c r="AD24" s="1"/>
     </row>
-    <row r="25" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>860</v>
       </c>
@@ -25847,7 +25846,7 @@
       </c>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" spans="1:30" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" ht="36" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>861</v>
       </c>
@@ -25896,7 +25895,7 @@
       </c>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="1:30" ht="46" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" ht="48" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>862</v>
       </c>
@@ -25945,7 +25944,7 @@
       </c>
       <c r="AD27" s="1"/>
     </row>
-    <row r="28" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>863</v>
       </c>
@@ -25994,7 +25993,7 @@
       </c>
       <c r="AD28" s="1"/>
     </row>
-    <row r="29" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>864</v>
       </c>
@@ -26043,7 +26042,7 @@
       </c>
       <c r="AD29" s="1"/>
     </row>
-    <row r="30" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>865</v>
       </c>
@@ -26092,7 +26091,7 @@
       </c>
       <c r="AD30" s="1"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>866</v>
       </c>
@@ -26141,7 +26140,7 @@
       </c>
       <c r="AD31" s="1"/>
     </row>
-    <row r="32" spans="1:30" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:30" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>867</v>
       </c>
@@ -26178,7 +26177,7 @@
       </c>
       <c r="AD32" s="1"/>
     </row>
-    <row r="33" spans="1:30" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>868</v>
       </c>
@@ -26215,7 +26214,7 @@
       </c>
       <c r="AD33" s="1"/>
     </row>
-    <row r="34" spans="1:30" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>895</v>
       </c>
@@ -26252,7 +26251,7 @@
       </c>
       <c r="AD34" s="1"/>
     </row>
-    <row r="35" spans="1:30" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:30" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>896</v>
       </c>
@@ -26289,7 +26288,7 @@
       </c>
       <c r="AD35" s="1"/>
     </row>
-    <row r="36" spans="1:30" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:30" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>897</v>
       </c>
@@ -26326,7 +26325,7 @@
       </c>
       <c r="AD36" s="1"/>
     </row>
-    <row r="37" spans="1:30" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:30" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>898</v>
       </c>
@@ -26363,7 +26362,7 @@
       </c>
       <c r="AD37" s="1"/>
     </row>
-    <row r="38" spans="1:30" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:30" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>899</v>
       </c>
@@ -26400,7 +26399,7 @@
       </c>
       <c r="AD38" s="1"/>
     </row>
-    <row r="39" spans="1:30" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:30" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>900</v>
       </c>
@@ -26437,7 +26436,7 @@
       </c>
       <c r="AD39" s="1"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>901</v>
       </c>
@@ -26470,7 +26469,7 @@
       </c>
       <c r="AD40" s="1"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="AC41" s="7">
         <f>+(L41+M41)-O41-R41-U41-X41-AA41</f>
         <v>0</v>
@@ -26478,14 +26477,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -26496,6 +26487,14 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AC3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26507,96 +26506,96 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:AD49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.1796875" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.453125" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.42578125" customWidth="1"/>
     <col min="8" max="8" width="45" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
-    <col min="12" max="13" width="8.81640625" style="57"/>
-    <col min="14" max="14" width="10.453125" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="12" max="13" width="8.85546875" style="57"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" customWidth="1"/>
+    <col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="L1"/>
       <c r="M1"/>
     </row>
-    <row r="2" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="229" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="229" t="s">
+    <row r="2" spans="1:30" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="230" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="230" t="s">
         <v>1044</v>
       </c>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="231" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="229" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="229" t="s">
+      <c r="G2" s="230" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="229" t="s">
+      <c r="H2" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="229" t="s">
+      <c r="I2" s="230" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="229" t="s">
+      <c r="J2" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="229" t="s">
+      <c r="K2" s="230" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="228" t="s">
+      <c r="L2" s="234" t="s">
         <v>1260</v>
       </c>
-      <c r="M2" s="233" t="s">
+      <c r="M2" s="228" t="s">
         <v>1261</v>
       </c>
-      <c r="N2" s="230" t="s">
+      <c r="N2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="231"/>
-      <c r="P2" s="232"/>
-      <c r="Q2" s="230" t="s">
+      <c r="O2" s="232"/>
+      <c r="P2" s="233"/>
+      <c r="Q2" s="231" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="231"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="230" t="s">
+      <c r="R2" s="232"/>
+      <c r="S2" s="233"/>
+      <c r="T2" s="231" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="231"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="230" t="s">
+      <c r="U2" s="232"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="231" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="231"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="230" t="s">
+      <c r="X2" s="232"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="231"/>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="229" t="s">
+      <c r="AA2" s="232"/>
+      <c r="AB2" s="233"/>
+      <c r="AC2" s="230" t="s">
         <v>14</v>
       </c>
-      <c r="AD2" s="229" t="s">
+      <c r="AD2" s="230" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="229"/>
-      <c r="B3" s="229"/>
+    <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="230"/>
+      <c r="B3" s="230"/>
       <c r="C3" s="18" t="s">
         <v>23</v>
       </c>
@@ -26606,14 +26605,14 @@
       <c r="E3" s="18" t="s">
         <v>1027</v>
       </c>
-      <c r="F3" s="229"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="229"/>
-      <c r="I3" s="229"/>
-      <c r="J3" s="229"/>
-      <c r="K3" s="229"/>
-      <c r="L3" s="228"/>
-      <c r="M3" s="234"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="230"/>
+      <c r="H3" s="230"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="234"/>
+      <c r="M3" s="229"/>
       <c r="N3" s="18" t="s">
         <v>1</v>
       </c>
@@ -26659,10 +26658,10 @@
       <c r="AB3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="AC3" s="229"/>
-      <c r="AD3" s="229"/>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AC3" s="230"/>
+      <c r="AD3" s="230"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>80</v>
       </c>
@@ -26711,7 +26710,7 @@
       </c>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>81</v>
       </c>
@@ -26760,7 +26759,7 @@
       </c>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>82</v>
       </c>
@@ -26809,7 +26808,7 @@
       </c>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>83</v>
       </c>
@@ -26858,7 +26857,7 @@
       </c>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>84</v>
       </c>
@@ -26905,7 +26904,7 @@
       </c>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>85</v>
       </c>
@@ -26952,7 +26951,7 @@
       </c>
       <c r="AD9" s="1"/>
     </row>
-    <row r="10" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>86</v>
       </c>
@@ -27001,7 +27000,7 @@
       </c>
       <c r="AD10" s="1"/>
     </row>
-    <row r="11" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>87</v>
       </c>
@@ -27050,7 +27049,7 @@
       </c>
       <c r="AD11" s="1"/>
     </row>
-    <row r="12" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>88</v>
       </c>
@@ -27099,7 +27098,7 @@
       </c>
       <c r="AD12" s="1"/>
     </row>
-    <row r="13" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>89</v>
       </c>
@@ -27148,7 +27147,7 @@
       </c>
       <c r="AD13" s="1"/>
     </row>
-    <row r="14" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>90</v>
       </c>
@@ -27197,7 +27196,7 @@
       </c>
       <c r="AD14" s="1"/>
     </row>
-    <row r="15" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>91</v>
       </c>
@@ -27246,7 +27245,7 @@
       </c>
       <c r="AD15" s="1"/>
     </row>
-    <row r="16" spans="1:30" ht="15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>92</v>
       </c>
@@ -27295,7 +27294,7 @@
       </c>
       <c r="AD16" s="1"/>
     </row>
-    <row r="17" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>93</v>
       </c>
@@ -27344,7 +27343,7 @@
       </c>
       <c r="AD17" s="3"/>
     </row>
-    <row r="18" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>94</v>
       </c>
@@ -27393,7 +27392,7 @@
       </c>
       <c r="AD18" s="3"/>
     </row>
-    <row r="19" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>95</v>
       </c>
@@ -27442,7 +27441,7 @@
       </c>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="1:30" ht="22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>96</v>
       </c>
@@ -27499,7 +27498,7 @@
       </c>
       <c r="AD20" s="8"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>97</v>
       </c>
@@ -27548,7 +27547,7 @@
       </c>
       <c r="AD21" s="1"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>98</v>
       </c>
@@ -27597,7 +27596,7 @@
       </c>
       <c r="AD22" s="1"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>99</v>
       </c>
@@ -27648,7 +27647,7 @@
       </c>
       <c r="AD23" s="1"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="201" t="s">
         <v>100</v>
       </c>
@@ -27707,7 +27706,7 @@
       </c>
       <c r="AD24" s="1"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>101</v>
       </c>
@@ -27750,7 +27749,7 @@
       </c>
       <c r="AD25" s="52"/>
     </row>
-    <row r="26" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>102</v>
       </c>
@@ -27799,7 +27798,7 @@
       </c>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>103</v>
       </c>
@@ -27848,7 +27847,7 @@
       </c>
       <c r="AD27" s="1"/>
     </row>
-    <row r="28" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>104</v>
       </c>
@@ -27897,7 +27896,7 @@
       </c>
       <c r="AD28" s="1"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>105</v>
       </c>
@@ -27946,7 +27945,7 @@
       </c>
       <c r="AD29" s="1"/>
     </row>
-    <row r="30" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>106</v>
       </c>
@@ -27995,7 +27994,7 @@
       </c>
       <c r="AD30" s="1"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>107</v>
       </c>
@@ -28044,7 +28043,7 @@
       </c>
       <c r="AD31" s="1"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>108</v>
       </c>
@@ -28093,7 +28092,7 @@
       </c>
       <c r="AD32" s="1"/>
     </row>
-    <row r="33" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>958</v>
       </c>
@@ -28142,7 +28141,7 @@
       </c>
       <c r="AD33" s="1"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>959</v>
       </c>
@@ -28191,7 +28190,7 @@
       </c>
       <c r="AD34" s="1"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>960</v>
       </c>
@@ -28230,7 +28229,7 @@
       </c>
       <c r="AD35" s="1"/>
     </row>
-    <row r="36" spans="1:30" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>961</v>
       </c>
@@ -28287,7 +28286,7 @@
       </c>
       <c r="AD36" s="1"/>
     </row>
-    <row r="37" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>962</v>
       </c>
@@ -28336,7 +28335,7 @@
       </c>
       <c r="AD37" s="1"/>
     </row>
-    <row r="38" spans="1:30" ht="23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:30" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="84" t="s">
         <v>963</v>
       </c>
@@ -28385,7 +28384,7 @@
       </c>
       <c r="AD38" s="1"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="84" t="s">
         <v>964</v>
       </c>
@@ -28434,7 +28433,7 @@
       </c>
       <c r="AD39" s="1"/>
     </row>
-    <row r="40" spans="1:30" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:30" ht="36" x14ac:dyDescent="0.25">
       <c r="A40" s="84" t="s">
         <v>965</v>
       </c>
@@ -28490,7 +28489,7 @@
       </c>
       <c r="AD40" s="1"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="84" t="s">
         <v>966</v>
       </c>
@@ -28535,7 +28534,7 @@
       </c>
       <c r="AD41" s="1"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="84" t="s">
         <v>967</v>
       </c>
@@ -28578,7 +28577,7 @@
       </c>
       <c r="AD42" s="1"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="84" t="s">
         <v>968</v>
       </c>
@@ -28615,7 +28614,7 @@
       </c>
       <c r="AD43" s="1"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="84" t="s">
         <v>969</v>
       </c>
@@ -28652,7 +28651,7 @@
       </c>
       <c r="AD44" s="1"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="84" t="s">
         <v>970</v>
       </c>
@@ -28689,7 +28688,7 @@
       </c>
       <c r="AD45" s="1"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="84" t="s">
         <v>1047</v>
       </c>
@@ -28726,7 +28725,7 @@
       </c>
       <c r="AD46" s="1"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="84" t="s">
         <v>1048</v>
       </c>
@@ -28763,7 +28762,7 @@
       </c>
       <c r="AD47" s="1"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="44"/>
@@ -28798,7 +28797,7 @@
       </c>
       <c r="AD48" s="1"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -28835,14 +28834,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -28853,6 +28844,14 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AC3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -28865,29 +28864,29 @@
     <tabColor rgb="FFEEEEDE"/>
   </sheetPr>
   <dimension ref="A1:AD18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.54296875" customWidth="1"/>
-    <col min="8" max="8" width="22.1796875" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.81640625" style="57"/>
-    <col min="14" max="14" width="10.453125" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" customWidth="1"/>
-    <col min="29" max="29" width="11.453125" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.85546875" style="57"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.42578125" customWidth="1"/>
+    <col min="29" max="29" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="L1"/>
       <c r="M1"/>
     </row>
-    <row r="2" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="228" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="228" t="s">
+    <row r="2" spans="1:30" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="234" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="234" t="s">
         <v>1044</v>
       </c>
       <c r="C2" s="235" t="s">
@@ -28895,28 +28894,28 @@
       </c>
       <c r="D2" s="236"/>
       <c r="E2" s="237"/>
-      <c r="F2" s="228" t="s">
+      <c r="F2" s="234" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="228" t="s">
+      <c r="G2" s="234" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="228" t="s">
+      <c r="H2" s="234" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="228" t="s">
+      <c r="I2" s="234" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="228" t="s">
+      <c r="J2" s="234" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="228" t="s">
+      <c r="K2" s="234" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="228" t="s">
+      <c r="L2" s="234" t="s">
         <v>1260</v>
       </c>
-      <c r="M2" s="233" t="s">
+      <c r="M2" s="228" t="s">
         <v>1261</v>
       </c>
       <c r="N2" s="235" t="s">
@@ -28944,14 +28943,14 @@
       </c>
       <c r="AA2" s="236"/>
       <c r="AB2" s="237"/>
-      <c r="AC2" s="228" t="s">
+      <c r="AC2" s="234" t="s">
         <v>14</v>
       </c>
-      <c r="AD2" s="215"/>
-    </row>
-    <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="228"/>
-      <c r="B3" s="228"/>
+      <c r="AD2" s="219"/>
+    </row>
+    <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="234"/>
+      <c r="B3" s="234"/>
       <c r="C3" s="45" t="s">
         <v>23</v>
       </c>
@@ -28961,14 +28960,14 @@
       <c r="E3" s="45" t="s">
         <v>1026</v>
       </c>
-      <c r="F3" s="228"/>
-      <c r="G3" s="228"/>
-      <c r="H3" s="228"/>
-      <c r="I3" s="228"/>
-      <c r="J3" s="228"/>
-      <c r="K3" s="228"/>
-      <c r="L3" s="228"/>
-      <c r="M3" s="234"/>
+      <c r="F3" s="234"/>
+      <c r="G3" s="234"/>
+      <c r="H3" s="234"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
+      <c r="M3" s="229"/>
       <c r="N3" s="45" t="s">
         <v>1</v>
       </c>
@@ -29014,10 +29013,10 @@
       <c r="AB3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="AC3" s="228"/>
-      <c r="AD3" s="215"/>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AC3" s="234"/>
+      <c r="AD3" s="219"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
         <v>1002</v>
       </c>
@@ -29060,7 +29059,7 @@
       </c>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="46" t="s">
         <v>1003</v>
       </c>
@@ -29099,7 +29098,7 @@
       </c>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="46" t="s">
         <v>1004</v>
       </c>
@@ -29142,7 +29141,7 @@
       </c>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="46" t="s">
         <v>1005</v>
       </c>
@@ -29181,7 +29180,7 @@
       </c>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="1:30" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A8" s="46" t="s">
         <v>1006</v>
       </c>
@@ -29228,7 +29227,7 @@
       </c>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="46" t="s">
         <v>1007</v>
       </c>
@@ -29265,7 +29264,7 @@
       </c>
       <c r="AD9" s="1"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="46" t="s">
         <v>1008</v>
       </c>
@@ -29314,7 +29313,7 @@
       </c>
       <c r="AD10" s="1"/>
     </row>
-    <row r="11" spans="1:30" ht="21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A11" s="46" t="s">
         <v>1009</v>
       </c>
@@ -29361,7 +29360,7 @@
       </c>
       <c r="AD11" s="1"/>
     </row>
-    <row r="12" spans="1:30" ht="21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A12" s="46" t="s">
         <v>1010</v>
       </c>
@@ -29412,7 +29411,7 @@
       </c>
       <c r="AD12" s="1"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="46" t="s">
         <v>1011</v>
       </c>
@@ -29449,7 +29448,7 @@
       </c>
       <c r="AD13" s="1"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="46" t="s">
         <v>1012</v>
       </c>
@@ -29486,7 +29485,7 @@
       </c>
       <c r="AD14" s="1"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="46" t="s">
         <v>1013</v>
       </c>
@@ -29523,7 +29522,7 @@
       </c>
       <c r="AD15" s="1"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="46" t="s">
         <v>1014</v>
       </c>
@@ -29560,7 +29559,7 @@
       </c>
       <c r="AD16" s="1"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="46" t="s">
         <v>1015</v>
       </c>
@@ -29597,7 +29596,7 @@
       </c>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -29634,14 +29633,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -29652,6 +29643,14 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AC3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29661,50 +29660,50 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AD9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.81640625" customWidth="1"/>
-    <col min="2" max="2" width="38.1796875" customWidth="1"/>
-    <col min="3" max="3" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="17.453125" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
-    <col min="12" max="12" width="8.81640625" style="162"/>
-    <col min="13" max="13" width="8.81640625" style="179"/>
+    <col min="1" max="1" width="6.85546875" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="162"/>
+    <col min="13" max="13" width="8.85546875" style="179"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="L1"/>
       <c r="M1"/>
     </row>
-    <row r="2" spans="1:30" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="238" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="238" t="s">
+    <row r="2" spans="1:30" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="241" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="241" t="s">
         <v>1044</v>
       </c>
-      <c r="C2" s="239" t="s">
+      <c r="C2" s="238" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="238" t="s">
+      <c r="D2" s="239"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="241" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="238" t="s">
+      <c r="G2" s="241" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="238" t="s">
+      <c r="H2" s="241" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="238" t="s">
+      <c r="I2" s="241" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="238" t="s">
+      <c r="J2" s="241" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="238" t="s">
+      <c r="K2" s="241" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="243" t="s">
@@ -29713,39 +29712,39 @@
       <c r="M2" s="244" t="s">
         <v>1261</v>
       </c>
-      <c r="N2" s="239" t="s">
+      <c r="N2" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="240"/>
-      <c r="P2" s="241"/>
-      <c r="Q2" s="239" t="s">
+      <c r="O2" s="239"/>
+      <c r="P2" s="240"/>
+      <c r="Q2" s="238" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="240"/>
-      <c r="S2" s="241"/>
-      <c r="T2" s="239" t="s">
+      <c r="R2" s="239"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="238" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="240"/>
-      <c r="V2" s="241"/>
-      <c r="W2" s="239" t="s">
+      <c r="U2" s="239"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="238" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="241"/>
-      <c r="Z2" s="239" t="s">
+      <c r="X2" s="239"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="238" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="240"/>
-      <c r="AB2" s="241"/>
-      <c r="AC2" s="238" t="s">
+      <c r="AA2" s="239"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="241" t="s">
         <v>14</v>
       </c>
       <c r="AD2" s="242"/>
     </row>
-    <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="238"/>
-      <c r="B3" s="238"/>
+    <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="241"/>
+      <c r="B3" s="241"/>
       <c r="C3" s="87" t="s">
         <v>23</v>
       </c>
@@ -29755,12 +29754,12 @@
       <c r="E3" s="87" t="s">
         <v>1026</v>
       </c>
-      <c r="F3" s="238"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="238"/>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="243"/>
       <c r="M3" s="245"/>
       <c r="N3" s="87" t="s">
@@ -29808,10 +29807,10 @@
       <c r="AB3" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="AC3" s="238"/>
+      <c r="AC3" s="241"/>
       <c r="AD3" s="242"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -29850,7 +29849,7 @@
       </c>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -29885,7 +29884,7 @@
       </c>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -29920,7 +29919,7 @@
       </c>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -29955,7 +29954,7 @@
       </c>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -29990,7 +29989,7 @@
       </c>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -30027,6 +30026,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="C2:E2"/>
     <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="AD2:AD3"/>
@@ -30040,11 +30044,6 @@
     <mergeCell ref="T2:V2"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="M2:M3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="C2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
